--- a/artfynd/A 49910-2022 artfynd.xlsx
+++ b/artfynd/A 49910-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49910-2022 artfynd.xlsx
+++ b/artfynd/A 49910-2022 artfynd.xlsx
@@ -1046,11 +1046,11 @@
         <v>118228759</v>
       </c>
       <c r="B5" t="n">
-        <v>57148</v>
+        <v>57235</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1060,11 +1060,6 @@
       </c>
       <c r="E5" t="n">
         <v>100100</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Bivråk</t>
-        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>

--- a/artfynd/A 49910-2022 artfynd.xlsx
+++ b/artfynd/A 49910-2022 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>118228759</v>
       </c>
       <c r="B5" t="n">
-        <v>57235</v>
+        <v>57239</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1060,6 +1060,11 @@
       </c>
       <c r="E5" t="n">
         <v>100100</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Bivråk</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>

--- a/artfynd/A 49910-2022 artfynd.xlsx
+++ b/artfynd/A 49910-2022 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>118228759</v>
       </c>
       <c r="B5" t="n">
-        <v>57239</v>
+        <v>57240</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 49910-2022 artfynd.xlsx
+++ b/artfynd/A 49910-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1169,6 +1169,318 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127501185</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98466</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Johannisfors, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>677770</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6695654</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Karolin Ring</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127504248</v>
+      </c>
+      <c r="B7" t="n">
+        <v>105396</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Johannisfors, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>677654</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6695662</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127504247</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98425</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Johannisfors, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>677842</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6695649</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49910-2022 artfynd.xlsx
+++ b/artfynd/A 49910-2022 artfynd.xlsx
@@ -1174,7 +1174,7 @@
         <v>127501185</v>
       </c>
       <c r="B6" t="n">
-        <v>98466</v>
+        <v>98470</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 49910-2022 artfynd.xlsx
+++ b/artfynd/A 49910-2022 artfynd.xlsx
@@ -1174,7 +1174,7 @@
         <v>127501185</v>
       </c>
       <c r="B6" t="n">
-        <v>98470</v>
+        <v>98471</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>127504248</v>
       </c>
       <c r="B7" t="n">
-        <v>105396</v>
+        <v>105398</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>127504247</v>
       </c>
       <c r="B8" t="n">
-        <v>98425</v>
+        <v>98426</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49910-2022 artfynd.xlsx
+++ b/artfynd/A 49910-2022 artfynd.xlsx
@@ -1174,7 +1174,7 @@
         <v>127501185</v>
       </c>
       <c r="B6" t="n">
-        <v>98471</v>
+        <v>98473</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>127504248</v>
       </c>
       <c r="B7" t="n">
-        <v>105398</v>
+        <v>105400</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>127504247</v>
       </c>
       <c r="B8" t="n">
-        <v>98426</v>
+        <v>98428</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49910-2022 artfynd.xlsx
+++ b/artfynd/A 49910-2022 artfynd.xlsx
@@ -1174,7 +1174,7 @@
         <v>127501185</v>
       </c>
       <c r="B6" t="n">
-        <v>98473</v>
+        <v>98479</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>127504248</v>
       </c>
       <c r="B7" t="n">
-        <v>105400</v>
+        <v>105406</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>127504247</v>
       </c>
       <c r="B8" t="n">
-        <v>98428</v>
+        <v>98434</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49910-2022 artfynd.xlsx
+++ b/artfynd/A 49910-2022 artfynd.xlsx
@@ -1174,7 +1174,7 @@
         <v>127501185</v>
       </c>
       <c r="B6" t="n">
-        <v>98479</v>
+        <v>98482</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>127504248</v>
       </c>
       <c r="B7" t="n">
-        <v>105406</v>
+        <v>105409</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>127504247</v>
       </c>
       <c r="B8" t="n">
-        <v>98434</v>
+        <v>98437</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49910-2022 artfynd.xlsx
+++ b/artfynd/A 49910-2022 artfynd.xlsx
@@ -1174,7 +1174,7 @@
         <v>127501185</v>
       </c>
       <c r="B6" t="n">
-        <v>98482</v>
+        <v>98490</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>127504248</v>
       </c>
       <c r="B7" t="n">
-        <v>105409</v>
+        <v>105417</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>127504247</v>
       </c>
       <c r="B8" t="n">
-        <v>98437</v>
+        <v>98445</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49910-2022 artfynd.xlsx
+++ b/artfynd/A 49910-2022 artfynd.xlsx
@@ -1174,7 +1174,7 @@
         <v>127501185</v>
       </c>
       <c r="B6" t="n">
-        <v>98490</v>
+        <v>98491</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>127504248</v>
       </c>
       <c r="B7" t="n">
-        <v>105417</v>
+        <v>105418</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>127504247</v>
       </c>
       <c r="B8" t="n">
-        <v>98445</v>
+        <v>98446</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49910-2022 artfynd.xlsx
+++ b/artfynd/A 49910-2022 artfynd.xlsx
@@ -1174,7 +1174,7 @@
         <v>127501185</v>
       </c>
       <c r="B6" t="n">
-        <v>98491</v>
+        <v>98492</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>127504248</v>
       </c>
       <c r="B7" t="n">
-        <v>105418</v>
+        <v>105419</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>127504247</v>
       </c>
       <c r="B8" t="n">
-        <v>98446</v>
+        <v>98447</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49910-2022 artfynd.xlsx
+++ b/artfynd/A 49910-2022 artfynd.xlsx
@@ -1174,7 +1174,7 @@
         <v>127501185</v>
       </c>
       <c r="B6" t="n">
-        <v>98492</v>
+        <v>98493</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>127504248</v>
       </c>
       <c r="B7" t="n">
-        <v>105419</v>
+        <v>105420</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>127504247</v>
       </c>
       <c r="B8" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49910-2022 artfynd.xlsx
+++ b/artfynd/A 49910-2022 artfynd.xlsx
@@ -1046,12 +1046,7 @@
         <v>118228759</v>
       </c>
       <c r="B5" t="n">
-        <v>57334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57790</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 49910-2022 artfynd.xlsx
+++ b/artfynd/A 49910-2022 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>118228759</v>
       </c>
       <c r="B5" t="n">
-        <v>57790</v>
+        <v>57792</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 49910-2022 artfynd.xlsx
+++ b/artfynd/A 49910-2022 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>118228759</v>
       </c>
       <c r="B5" t="n">
-        <v>57792</v>
+        <v>57797</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 49910-2022 artfynd.xlsx
+++ b/artfynd/A 49910-2022 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>118228759</v>
       </c>
       <c r="B5" t="n">
-        <v>57797</v>
+        <v>57799</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 49910-2022 artfynd.xlsx
+++ b/artfynd/A 49910-2022 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>118228759</v>
       </c>
       <c r="B5" t="n">
-        <v>57799</v>
+        <v>57833</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 49910-2022 artfynd.xlsx
+++ b/artfynd/A 49910-2022 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>118228759</v>
       </c>
       <c r="B5" t="n">
-        <v>57833</v>
+        <v>57834</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 49910-2022 artfynd.xlsx
+++ b/artfynd/A 49910-2022 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>118228759</v>
       </c>
       <c r="B5" t="n">
-        <v>57834</v>
+        <v>57838</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 49910-2022 artfynd.xlsx
+++ b/artfynd/A 49910-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99343468</v>
+        <v>99367841</v>
       </c>
       <c r="B2" t="n">
-        <v>57068</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56925</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103057</v>
+        <v>100045</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,19 +705,19 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>FM-3129-3-56, Upl</t>
+          <t>FM-46-3-84, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>677770.6990483192</v>
+        <v>677839</v>
       </c>
       <c r="R2" t="n">
-        <v>6695701.657121705</v>
+        <v>6695645</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,22 +744,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-05-18</t>
+          <t>2013-05-29</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>05:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-05-18</t>
+          <t>2013-05-29</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>05:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,15 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99343887</v>
+        <v>118228759</v>
       </c>
       <c r="B3" t="n">
-        <v>56859</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57860</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,21 +801,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103018</v>
+        <v>100100</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Bivråk</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Pernis apivorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -833,19 +823,31 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>FM-29-3-12, Upl</t>
+          <t>Y-korset, Storskäret, Kallrigafjärden, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>677768.971402412</v>
+        <v>677656</v>
       </c>
       <c r="R3" t="n">
-        <v>6695706.528511851</v>
+        <v>6695663</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,22 +871,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2013-05-14</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>04:34</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2013-05-14</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>04:34</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,31 +901,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mathias Andersson</t>
+          <t>Magnus Liljefors</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Mathias Andersson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Forsmark platsundersökning</t>
-        </is>
-      </c>
+          <t>Magnus Liljefors</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>118228766</v>
       </c>
       <c r="B4" t="n">
-        <v>57385</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,32 +1036,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118228759</v>
+        <v>99367830</v>
       </c>
       <c r="B5" t="n">
-        <v>57838</v>
+        <v>57295</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100100</v>
+        <v>102950</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bivråk</t>
+          <t>Strandskata</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pernis apivorus</t>
+          <t>Haematopus ostralegus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1076,31 +1069,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Y-korset, Storskäret, Kallrigafjärden, Upl</t>
+          <t>FM-46-3-84, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>677656</v>
+        <v>677839</v>
       </c>
       <c r="R5" t="n">
-        <v>6695663</v>
+        <v>6695645</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1124,22 +1105,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2018-05-31</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2018-05-31</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,44 +1135,48 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Magnus Liljefors</t>
+          <t>Mathias Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Liljefors</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127501185</v>
+        <v>99367837</v>
       </c>
       <c r="B6" t="n">
-        <v>98493</v>
+        <v>57369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219847</v>
+        <v>102961</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1199,23 +1184,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Johannisfors, Upl</t>
+          <t>FM-46-3-84, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>677770</v>
+        <v>677839</v>
       </c>
       <c r="R6" t="n">
-        <v>6695654</v>
+        <v>6695645</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1239,12 +1220,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2018-05-31</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2018-05-31</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,71 +1244,74 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Staffan Fridh</t>
+          <t>Mathias Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Karolin Ring</t>
+          <t>Via Mathias Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+          <t>Forsmark platsundersökning</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127504248</v>
+        <v>99333280</v>
       </c>
       <c r="B7" t="n">
-        <v>105420</v>
+        <v>57546</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221141</v>
+        <v>102963</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Johannisfors, Upl</t>
+          <t>FM-21870-2-52, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>677654</v>
+        <v>677473</v>
       </c>
       <c r="R7" t="n">
-        <v>6695662</v>
+        <v>6695542</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1341,12 +1335,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2007-06-18</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2007-06-18</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,64 +1365,68 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Staffan Fridh</t>
+          <t>Mathias Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Via Mathias Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+          <t>Forsmark platsundersökning</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127504247</v>
+        <v>99333303</v>
       </c>
       <c r="B8" t="n">
-        <v>98448</v>
+        <v>57569</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219798</v>
+        <v>102967</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Havstrut</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Larus marinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Johannisfors, Upl</t>
+          <t>FM-21855-5-14, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>677842</v>
+        <v>677846</v>
       </c>
       <c r="R8" t="n">
-        <v>6695649</v>
+        <v>6695735</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1442,12 +1450,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2007-06-18</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2007-06-18</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,15 +1480,1569 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>99333299</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58209</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102980</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ladusvala</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hirundo rustica</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>FM-21855-5-14, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>677846</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6695735</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2018-05-29</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2018-05-29</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>99333300</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58238</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>FM-21855-5-14, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>677846</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6695735</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2007-06-18</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2007-06-18</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>99343887</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>FM-29-3-12, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>677769</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6695707</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2013-05-14</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>04:34</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2013-05-14</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>04:34</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>99315946</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>FM-12850-4-9, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>677887</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6695635</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2002-05-07</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2002-05-07</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>99333305</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>FM-21855-5-14, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>677846</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6695735</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2007-06-18</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2007-06-18</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>99343884</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>FM-29-3-12, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>677769</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6695707</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2013-05-14</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2013-05-14</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>99315950</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58649</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103057</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Sävsparv</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Emberiza schoeniclus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>FM-12850-4-9, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>677887</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6695635</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2002-05-07</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2002-05-07</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>99343468</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58649</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103057</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Sävsparv</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Emberiza schoeniclus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>FM-3129-3-56, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>677771</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6695702</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2018-05-18</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2018-05-18</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>99367836</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58649</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103057</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Sävsparv</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Emberiza schoeniclus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>FM-46-3-84, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>677839</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6695645</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2018-05-31</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2018-05-31</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127504247</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Johannisfors, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>677842</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6695649</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
           <t>Staffan Fridh</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AX18" t="inlineStr">
         <is>
           <t>Veronica Lindström</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr">
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127501183</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Johannisfors, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>677841</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6695644</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Karolin Ring</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127501185</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Johannisfors, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>677770</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6695654</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Karolin Ring</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127504248</v>
+      </c>
+      <c r="B21" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Johannisfors, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>677654</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6695662</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127504249</v>
+      </c>
+      <c r="B22" t="n">
+        <v>104641</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Johannisfors, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>677451</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6695489</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>

--- a/artfynd/A 49910-2022 artfynd.xlsx
+++ b/artfynd/A 49910-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99367841</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118228759</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1033,6 +1048,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118228766</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1148,6 +1168,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99367830</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1263,6 +1288,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99367837</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1378,6 +1408,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99333280</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1493,6 +1528,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99333303</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1608,6 +1648,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99333299</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1723,6 +1768,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99333300</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1838,6 +1888,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99343887</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1953,6 +2008,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99315946</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2068,6 +2128,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99333305</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2183,6 +2248,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99343884</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2298,6 +2368,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99315950</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2413,6 +2488,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99343468</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2528,6 +2608,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99367836</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2627,6 +2712,11 @@
       <c r="AY18" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127504247</t>
         </is>
       </c>
     </row>
@@ -2739,6 +2829,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127501183</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2849,6 +2944,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127501185</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2950,6 +3050,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127504248</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3047,8 +3152,36 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127504249</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>